--- a/ig/StructureDefinition-as-organization.xlsx
+++ b/ig/StructureDefinition-as-organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T13:25:16+00:00</t>
+    <t>2024-04-25T11:50:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1074,7 +1074,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="http://interopsante.org/CodeSystem/fr-v2-0203"/&gt;
+    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203"/&gt;
     &lt;code value="IDNST"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1306,7 +1306,7 @@
     <t>Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
-    <t>http://interopsante.org/CodeSystem/fr-v2-0203</t>
+    <t>https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203</t>
   </si>
   <si>
     <t>Coding.system</t>
@@ -1451,7 +1451,7 @@
     <t>Organization.identifier:sirene.system</t>
   </si>
   <si>
-    <t>http://sirene.fr</t>
+    <t>https://sirene.fr</t>
   </si>
   <si>
     <t>Organization.identifier:sirene.value</t>
@@ -1529,7 +1529,7 @@
     <t>Organization.identifier:finess.system</t>
   </si>
   <si>
-    <t>http://finess.esante.gouv.fr</t>
+    <t>https://finess.esante.gouv.fr</t>
   </si>
   <si>
     <t>Organization.identifier:finess.value</t>
@@ -1564,7 +1564,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="http://interopsante.org/CodeSystem/fr-v2-0203"/&gt;
+    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203"/&gt;
     &lt;code value="INTRN"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>

--- a/ig/StructureDefinition-as-organization.xlsx
+++ b/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T11:50:43+00:00</t>
+    <t>2024-04-26T07:42:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
